--- a/artfynd/A 1212-2023 artfynd.xlsx
+++ b/artfynd/A 1212-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 1212-2023 artfynd.xlsx
+++ b/artfynd/A 1212-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>73933037</v>
+        <v>106540424</v>
       </c>
       <c r="B2" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,42 +686,47 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219798</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lilludden, Srm</t>
+          <t>Torö, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>663557.2415199723</v>
+        <v>663575</v>
       </c>
       <c r="R2" t="n">
-        <v>6526297.491265481</v>
+        <v>6526259</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,22 +750,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2015-08-19</t>
+          <t>2023-02-08</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2015-08-19</t>
+          <t>2023-02-08</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,34 +774,28 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Karin Kjellberg</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Karin Kjellberg</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>106543433</v>
+        <v>106544211</v>
       </c>
       <c r="B3" t="n">
-        <v>89940</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -809,26 +803,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3884</v>
+        <v>210</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -838,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>663450.7640543403</v>
+        <v>663455</v>
       </c>
       <c r="R3" t="n">
-        <v>6526299.19828214</v>
+        <v>6526304</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -873,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -883,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,15 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>106543671</v>
+        <v>107344650</v>
       </c>
       <c r="B4" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -926,35 +920,44 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>210</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Torö, Srm</t>
+          <t>Lilla Kurtorp, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>663442.8608611808</v>
+        <v>663404</v>
       </c>
       <c r="R4" t="n">
-        <v>6526301.972304684</v>
+        <v>6526246</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -981,22 +984,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-02-08</t>
+          <t>2023-03-18</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-02-08</t>
+          <t>2023-03-18</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,15 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>106541278</v>
+        <v>115806420</v>
       </c>
       <c r="B5" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1039,35 +1037,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>2569</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Torö, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>663524.0972955248</v>
+        <v>663575</v>
       </c>
       <c r="R5" t="n">
-        <v>6526271.21734459</v>
+        <v>6526259</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1094,22 +1091,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-02-08</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-02-08</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,15 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>106540424</v>
+        <v>115806895</v>
       </c>
       <c r="B6" t="n">
-        <v>93235</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97394</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1152,44 +1144,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>210</v>
+        <v>2590</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Torö, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>663575.4651632368</v>
+        <v>663575</v>
       </c>
       <c r="R6" t="n">
-        <v>6526259.404620979</v>
+        <v>6526259</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1216,22 +1198,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-02-08</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-02-08</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1258,15 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>106544211</v>
+        <v>115806366</v>
       </c>
       <c r="B7" t="n">
-        <v>93235</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1274,44 +1251,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>210</v>
+        <v>2810</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Torö, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>663454.7557019126</v>
+        <v>663575</v>
       </c>
       <c r="R7" t="n">
-        <v>6526302.994111993</v>
+        <v>6526259</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1338,22 +1305,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-02-08</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-02-08</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1380,15 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>107344722</v>
+        <v>106543433</v>
       </c>
       <c r="B8" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92497</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1396,24 +1358,28 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>3884</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Quél.) Domański &amp; Orlicz</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1421,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>663464.4186349885</v>
+        <v>663451</v>
       </c>
       <c r="R8" t="n">
-        <v>6526246.410391441</v>
+        <v>6526299</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1451,22 +1417,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-03-18</t>
+          <t>2023-02-08</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-03-18</t>
+          <t>2023-02-08</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1493,15 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>107344650</v>
+        <v>106544564</v>
       </c>
       <c r="B9" t="n">
-        <v>93235</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92497</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1509,44 +1470,44 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>210</v>
+        <v>3884</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>kapslar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lilla Kurtorp, Srm</t>
+          <t>Torö, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>663403.7321096973</v>
+        <v>663636</v>
       </c>
       <c r="R9" t="n">
-        <v>6526245.395232748</v>
+        <v>6526244</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1573,22 +1534,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-03-18</t>
+          <t>2023-02-08</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-03-18</t>
+          <t>2023-02-08</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1615,37 +1576,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>115806366</v>
+        <v>115807508</v>
       </c>
       <c r="B10" t="n">
-        <v>94069</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2810</v>
+        <v>6426</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1690,7 +1646,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1700,7 +1656,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1730,16 +1686,11 @@
         <v>115808153</v>
       </c>
       <c r="B11" t="n">
-        <v>109757</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111390</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1839,15 +1790,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>115806420</v>
+        <v>73933037</v>
       </c>
       <c r="B12" t="n">
-        <v>95923</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1855,37 +1801,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2569</v>
+        <v>219798</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Torö, Srm</t>
+          <t>Lilludden, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>663575</v>
+        <v>663557</v>
       </c>
       <c r="R12" t="n">
-        <v>6526259</v>
+        <v>6526297</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1909,22 +1860,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>10:13</t>
+          <t>2015-08-19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>10:13</t>
+          <t>2015-08-19</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1933,55 +1874,51 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Karin Kjellberg</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Karin Kjellberg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>115806895</v>
+        <v>115808774</v>
       </c>
       <c r="B13" t="n">
-        <v>95242</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2590</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2026,7 +1963,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2036,7 +1973,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2063,15 +2000,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>115807508</v>
+        <v>106541278</v>
       </c>
       <c r="B14" t="n">
-        <v>74585</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2079,34 +2011,35 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6426</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Torö, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>663575</v>
+        <v>663524</v>
       </c>
       <c r="R14" t="n">
-        <v>6526259</v>
+        <v>6526271</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2133,22 +2066,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>2023-02-08</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>2023-02-08</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2175,50 +2108,46 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>115808774</v>
+        <v>106543671</v>
       </c>
       <c r="B15" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Torö, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>663575</v>
+        <v>663443</v>
       </c>
       <c r="R15" t="n">
-        <v>6526259</v>
+        <v>6526302</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2245,22 +2174,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>2023-02-08</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>2023-02-08</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2287,15 +2216,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>115806651</v>
+        <v>107344722</v>
       </c>
       <c r="B16" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2321,16 +2245,17 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Torö, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>663575</v>
+        <v>663465</v>
       </c>
       <c r="R16" t="n">
-        <v>6526259</v>
+        <v>6526246</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2357,22 +2282,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>2023-03-18</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>2023-03-18</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2396,6 +2321,113 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>115806651</v>
+      </c>
+      <c r="B17" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Torö, Srm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>663575</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6526259</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Nynäshamn</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Torö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-04-09</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-04-09</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 1212-2023 artfynd.xlsx
+++ b/artfynd/A 1212-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,6 +794,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106540424</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -906,6 +916,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106544211</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1023,6 +1038,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107344650</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1130,6 +1150,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115806420</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1237,6 +1262,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115806895</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1344,6 +1374,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115806366</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1456,6 +1491,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106543433</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1573,6 +1613,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106544564</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1680,6 +1725,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115807508</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1787,6 +1837,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115808153</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1890,6 +1945,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73933037</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1997,6 +2057,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115808774</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2105,6 +2170,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106541278</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2213,6 +2283,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106543671</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2321,6 +2396,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107344722</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2428,8 +2508,31 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115806651</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>